--- a/output/yearly_total_coral_cover_iteration_36_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_36_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.250998329894622</v>
+        <v>1.25302073016537</v>
       </c>
       <c r="C3" t="n">
-        <v>4.62181970048497</v>
+        <v>4.586349155930533</v>
       </c>
       <c r="D3" t="n">
-        <v>6.058301363240931</v>
+        <v>6.078918065030114</v>
       </c>
       <c r="E3" t="n">
-        <v>11.93111939362052</v>
+        <v>11.91828795112602</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.369027232154166</v>
+        <v>1.383245146890223</v>
       </c>
       <c r="C4" t="n">
-        <v>5.083166918912041</v>
+        <v>4.997727158151583</v>
       </c>
       <c r="D4" t="n">
-        <v>6.375780249597669</v>
+        <v>6.414746075741408</v>
       </c>
       <c r="E4" t="n">
-        <v>12.82797440066388</v>
+        <v>12.79571838078321</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.527272874987949</v>
+        <v>1.567140514585361</v>
       </c>
       <c r="C5" t="n">
-        <v>5.686453313131547</v>
+        <v>5.490976881265813</v>
       </c>
       <c r="D5" t="n">
-        <v>6.691852748019717</v>
+        <v>6.798609821338461</v>
       </c>
       <c r="E5" t="n">
-        <v>13.90557893613921</v>
+        <v>13.85672721718964</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.705110917473706</v>
+        <v>1.779192986224547</v>
       </c>
       <c r="C6" t="n">
-        <v>6.429043056665687</v>
+        <v>6.102482541926577</v>
       </c>
       <c r="D6" t="n">
-        <v>7.012425062829246</v>
+        <v>7.172082581076599</v>
       </c>
       <c r="E6" t="n">
-        <v>15.14657903696864</v>
+        <v>15.05375810922772</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.905850597917661</v>
+        <v>2.02027336349958</v>
       </c>
       <c r="C7" t="n">
-        <v>7.287198418225882</v>
+        <v>6.835743132345683</v>
       </c>
       <c r="D7" t="n">
-        <v>7.360965600170107</v>
+        <v>7.537704991291621</v>
       </c>
       <c r="E7" t="n">
-        <v>16.55401461631365</v>
+        <v>16.39372148713688</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.145462448481578</v>
+        <v>1.250507473155151</v>
       </c>
       <c r="C8" t="n">
-        <v>4.927153062901487</v>
+        <v>4.504346081744391</v>
       </c>
       <c r="D8" t="n">
-        <v>5.600498915775627</v>
+        <v>5.849696905153229</v>
       </c>
       <c r="E8" t="n">
-        <v>11.67311442715869</v>
+        <v>11.60455046005277</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.429546621095452</v>
+        <v>1.581310222626497</v>
       </c>
       <c r="C9" t="n">
-        <v>5.993701708589813</v>
+        <v>5.452963829234001</v>
       </c>
       <c r="D9" t="n">
-        <v>6.074724634398955</v>
+        <v>6.451147068839879</v>
       </c>
       <c r="E9" t="n">
-        <v>13.49797296408422</v>
+        <v>13.48542112070038</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.725366084660965</v>
+        <v>1.937479556710785</v>
       </c>
       <c r="C10" t="n">
-        <v>7.279816128773289</v>
+        <v>6.524759464653163</v>
       </c>
       <c r="D10" t="n">
-        <v>6.630884473425088</v>
+        <v>7.021440408198809</v>
       </c>
       <c r="E10" t="n">
-        <v>15.63606668685934</v>
+        <v>15.48367942956276</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.033728562950012</v>
+        <v>2.303228847400677</v>
       </c>
       <c r="C11" t="n">
-        <v>8.711478301338481</v>
+        <v>7.691018177155221</v>
       </c>
       <c r="D11" t="n">
-        <v>7.152008725271064</v>
+        <v>7.572095698791991</v>
       </c>
       <c r="E11" t="n">
-        <v>17.89721558955956</v>
+        <v>17.56634272334789</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.349147209827812</v>
+        <v>2.690627122408915</v>
       </c>
       <c r="C12" t="n">
-        <v>10.2985309768699</v>
+        <v>8.928179277926548</v>
       </c>
       <c r="D12" t="n">
-        <v>7.659661487324341</v>
+        <v>8.093680590660981</v>
       </c>
       <c r="E12" t="n">
-        <v>20.30733967402205</v>
+        <v>19.71248699099644</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.654853746458763</v>
+        <v>3.073427958866223</v>
       </c>
       <c r="C13" t="n">
-        <v>12.01090314854718</v>
+        <v>10.28966054808578</v>
       </c>
       <c r="D13" t="n">
-        <v>8.132449464517867</v>
+        <v>8.619360505392612</v>
       </c>
       <c r="E13" t="n">
-        <v>22.79820635952381</v>
+        <v>21.98244901234461</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.53668059407232</v>
+        <v>1.778809030370711</v>
       </c>
       <c r="C14" t="n">
-        <v>8.538456133375359</v>
+        <v>7.311359860360228</v>
       </c>
       <c r="D14" t="n">
-        <v>6.189556028625568</v>
+        <v>6.531960175435728</v>
       </c>
       <c r="E14" t="n">
-        <v>16.26469275607325</v>
+        <v>15.62212906616667</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.567694004049477</v>
+        <v>1.849269063104504</v>
       </c>
       <c r="C15" t="n">
-        <v>9.392763168133891</v>
+        <v>7.893182819805059</v>
       </c>
       <c r="D15" t="n">
-        <v>6.209495324498821</v>
+        <v>6.580163987714246</v>
       </c>
       <c r="E15" t="n">
-        <v>17.16995249668219</v>
+        <v>16.32261587062381</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.812954215524415</v>
+        <v>2.177742209991402</v>
       </c>
       <c r="C16" t="n">
-        <v>11.25600250106983</v>
+        <v>9.377212284498622</v>
       </c>
       <c r="D16" t="n">
-        <v>6.634660802776988</v>
+        <v>7.134360566761572</v>
       </c>
       <c r="E16" t="n">
-        <v>19.70361751937123</v>
+        <v>18.6893150612516</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.448362570598277</v>
+        <v>1.765761603381271</v>
       </c>
       <c r="C17" t="n">
-        <v>10.54566876713909</v>
+        <v>8.755108216748546</v>
       </c>
       <c r="D17" t="n">
-        <v>6.13260484430221</v>
+        <v>6.664594290279473</v>
       </c>
       <c r="E17" t="n">
-        <v>18.12663618203958</v>
+        <v>17.18546411040929</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.637525718252552</v>
+        <v>2.040641143093335</v>
       </c>
       <c r="C18" t="n">
-        <v>12.39952259202243</v>
+        <v>10.30724151968571</v>
       </c>
       <c r="D18" t="n">
-        <v>6.512816095202916</v>
+        <v>7.120164494958162</v>
       </c>
       <c r="E18" t="n">
-        <v>20.5498644054779</v>
+        <v>19.46804715773721</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.630948008634099</v>
+        <v>2.071988347289936</v>
       </c>
       <c r="C19" t="n">
-        <v>13.34406205827828</v>
+        <v>11.11882289435542</v>
       </c>
       <c r="D19" t="n">
-        <v>6.570788297138691</v>
+        <v>7.238641807906667</v>
       </c>
       <c r="E19" t="n">
-        <v>21.54579836405107</v>
+        <v>20.42945304955202</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.801958641236851</v>
+        <v>2.340692693942288</v>
       </c>
       <c r="C20" t="n">
-        <v>15.46888806701078</v>
+        <v>12.86159196650323</v>
       </c>
       <c r="D20" t="n">
-        <v>7.026643208651612</v>
+        <v>7.692081620067142</v>
       </c>
       <c r="E20" t="n">
-        <v>24.29748991689924</v>
+        <v>22.89436628051266</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.064037796816778</v>
+        <v>1.410771451002667</v>
       </c>
       <c r="C21" t="n">
-        <v>11.43776327103408</v>
+        <v>9.548301456917713</v>
       </c>
       <c r="D21" t="n">
-        <v>5.851255587219161</v>
+        <v>6.400494340360039</v>
       </c>
       <c r="E21" t="n">
-        <v>18.35305665507002</v>
+        <v>17.35956724828042</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_36_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_36_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.25302073016537</v>
+        <v>1.25843016001577</v>
       </c>
       <c r="C3" t="n">
-        <v>4.586349155930533</v>
+        <v>4.673479264682437</v>
       </c>
       <c r="D3" t="n">
-        <v>6.078918065030114</v>
+        <v>6.048464251244378</v>
       </c>
       <c r="E3" t="n">
-        <v>11.91828795112602</v>
+        <v>11.98037367594259</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.383245146890223</v>
+        <v>1.382449076598975</v>
       </c>
       <c r="C4" t="n">
-        <v>4.997727158151583</v>
+        <v>5.240202239280555</v>
       </c>
       <c r="D4" t="n">
-        <v>6.414746075741408</v>
+        <v>6.324129507094975</v>
       </c>
       <c r="E4" t="n">
-        <v>12.79571838078321</v>
+        <v>12.9467808229745</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.567140514585361</v>
+        <v>1.543861572634867</v>
       </c>
       <c r="C5" t="n">
-        <v>5.490976881265813</v>
+        <v>5.947614402290789</v>
       </c>
       <c r="D5" t="n">
-        <v>6.798609821338461</v>
+        <v>6.589754006152781</v>
       </c>
       <c r="E5" t="n">
-        <v>13.85672721718964</v>
+        <v>14.08122998107844</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.779192986224547</v>
+        <v>1.727474454713992</v>
       </c>
       <c r="C6" t="n">
-        <v>6.102482541926577</v>
+        <v>6.821691875901328</v>
       </c>
       <c r="D6" t="n">
-        <v>7.172082581076599</v>
+        <v>6.851072610912219</v>
       </c>
       <c r="E6" t="n">
-        <v>15.05375810922772</v>
+        <v>15.40023894152754</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.02027336349958</v>
+        <v>1.946997408990845</v>
       </c>
       <c r="C7" t="n">
-        <v>6.835743132345683</v>
+        <v>7.862417781281783</v>
       </c>
       <c r="D7" t="n">
-        <v>7.537704991291621</v>
+        <v>7.164541217658655</v>
       </c>
       <c r="E7" t="n">
-        <v>16.39372148713688</v>
+        <v>16.97395640793128</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.250507473155151</v>
+        <v>1.176493514025439</v>
       </c>
       <c r="C8" t="n">
-        <v>4.504346081744391</v>
+        <v>5.499198893409406</v>
       </c>
       <c r="D8" t="n">
-        <v>5.849696905153229</v>
+        <v>5.354536932625349</v>
       </c>
       <c r="E8" t="n">
-        <v>11.60455046005277</v>
+        <v>12.03022934006019</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.581310222626497</v>
+        <v>1.477173753801316</v>
       </c>
       <c r="C9" t="n">
-        <v>5.452963829234001</v>
+        <v>6.78363695600816</v>
       </c>
       <c r="D9" t="n">
-        <v>6.451147068839879</v>
+        <v>5.750621659227147</v>
       </c>
       <c r="E9" t="n">
-        <v>13.48542112070038</v>
+        <v>14.01143236903662</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.937479556710785</v>
+        <v>1.79646861530909</v>
       </c>
       <c r="C10" t="n">
-        <v>6.524759464653163</v>
+        <v>8.258904885347199</v>
       </c>
       <c r="D10" t="n">
-        <v>7.021440408198809</v>
+        <v>6.140876723851357</v>
       </c>
       <c r="E10" t="n">
-        <v>15.48367942956276</v>
+        <v>16.19625022450765</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.303228847400677</v>
+        <v>2.132300036335171</v>
       </c>
       <c r="C11" t="n">
-        <v>7.691018177155221</v>
+        <v>9.838521940165897</v>
       </c>
       <c r="D11" t="n">
-        <v>7.572095698791991</v>
+        <v>6.508057546410671</v>
       </c>
       <c r="E11" t="n">
-        <v>17.56634272334789</v>
+        <v>18.47887952291174</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.690627122408915</v>
+        <v>2.476699598053225</v>
       </c>
       <c r="C12" t="n">
-        <v>8.928179277926548</v>
+        <v>11.53003969861251</v>
       </c>
       <c r="D12" t="n">
-        <v>8.093680590660981</v>
+        <v>6.855018916782383</v>
       </c>
       <c r="E12" t="n">
-        <v>19.71248699099644</v>
+        <v>20.86175821344812</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.073427958866223</v>
+        <v>2.814345999524695</v>
       </c>
       <c r="C13" t="n">
-        <v>10.28966054808578</v>
+        <v>13.28915698231975</v>
       </c>
       <c r="D13" t="n">
-        <v>8.619360505392612</v>
+        <v>7.32220485336226</v>
       </c>
       <c r="E13" t="n">
-        <v>21.98244901234461</v>
+        <v>23.42570783520671</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.778809030370711</v>
+        <v>1.621179618976843</v>
       </c>
       <c r="C14" t="n">
-        <v>7.311359860360228</v>
+        <v>9.349497546807733</v>
       </c>
       <c r="D14" t="n">
-        <v>6.531960175435728</v>
+        <v>5.557654118787108</v>
       </c>
       <c r="E14" t="n">
-        <v>15.62212906616667</v>
+        <v>16.52833128457168</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.849269063104504</v>
+        <v>1.673879835740812</v>
       </c>
       <c r="C15" t="n">
-        <v>7.893182819805059</v>
+        <v>10.15700466850482</v>
       </c>
       <c r="D15" t="n">
-        <v>6.580163987714246</v>
+        <v>5.51247408943767</v>
       </c>
       <c r="E15" t="n">
-        <v>16.32261587062381</v>
+        <v>17.3433585936833</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.177742209991402</v>
+        <v>1.949937472697972</v>
       </c>
       <c r="C16" t="n">
-        <v>9.377212284498622</v>
+        <v>12.04119449744938</v>
       </c>
       <c r="D16" t="n">
-        <v>7.134360566761572</v>
+        <v>5.926054944805725</v>
       </c>
       <c r="E16" t="n">
-        <v>18.6893150612516</v>
+        <v>19.91718691495308</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.765761603381271</v>
+        <v>1.568508854644002</v>
       </c>
       <c r="C17" t="n">
-        <v>8.755108216748546</v>
+        <v>11.08725970566389</v>
       </c>
       <c r="D17" t="n">
-        <v>6.664594290279473</v>
+        <v>5.455395277912761</v>
       </c>
       <c r="E17" t="n">
-        <v>17.18546411040929</v>
+        <v>18.11116383822065</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.040641143093335</v>
+        <v>1.792376783643402</v>
       </c>
       <c r="C18" t="n">
-        <v>10.30724151968571</v>
+        <v>13.0200067760605</v>
       </c>
       <c r="D18" t="n">
-        <v>7.120164494958162</v>
+        <v>5.803660458517275</v>
       </c>
       <c r="E18" t="n">
-        <v>19.46804715773721</v>
+        <v>20.61604401822117</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.071988347289936</v>
+        <v>1.799396279728767</v>
       </c>
       <c r="C19" t="n">
-        <v>11.11882289435542</v>
+        <v>13.99512768330364</v>
       </c>
       <c r="D19" t="n">
-        <v>7.238641807906667</v>
+        <v>5.854662251752896</v>
       </c>
       <c r="E19" t="n">
-        <v>20.42945304955202</v>
+        <v>21.6491862147853</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.340692693942288</v>
+        <v>2.004571732439307</v>
       </c>
       <c r="C20" t="n">
-        <v>12.86159196650323</v>
+        <v>16.1722121223332</v>
       </c>
       <c r="D20" t="n">
-        <v>7.692081620067142</v>
+        <v>6.254979695636576</v>
       </c>
       <c r="E20" t="n">
-        <v>22.89436628051266</v>
+        <v>24.43176355040908</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.410771451002667</v>
+        <v>1.190388726353343</v>
       </c>
       <c r="C21" t="n">
-        <v>9.548301456917713</v>
+        <v>11.96747506233749</v>
       </c>
       <c r="D21" t="n">
-        <v>6.400494340360039</v>
+        <v>5.202290902280891</v>
       </c>
       <c r="E21" t="n">
-        <v>17.35956724828042</v>
+        <v>18.36015469097173</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_36_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_36_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.25843016001577</v>
+        <v>2.583017001665058</v>
       </c>
       <c r="C3" t="n">
-        <v>4.673479264682437</v>
+        <v>7.672129676073353</v>
       </c>
       <c r="D3" t="n">
-        <v>6.048464251244378</v>
+        <v>8.138548828584886</v>
       </c>
       <c r="E3" t="n">
-        <v>11.98037367594259</v>
+        <v>18.3936955063233</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.382449076598975</v>
+        <v>1.066464419132399</v>
       </c>
       <c r="C4" t="n">
-        <v>5.240202239280555</v>
+        <v>4.472175198458284</v>
       </c>
       <c r="D4" t="n">
-        <v>6.324129507094975</v>
+        <v>5.673422576269437</v>
       </c>
       <c r="E4" t="n">
-        <v>12.9467808229745</v>
+        <v>11.21206219386012</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.543861572634867</v>
+        <v>1.17053811453008</v>
       </c>
       <c r="C5" t="n">
-        <v>5.947614402290789</v>
+        <v>5.134667578747651</v>
       </c>
       <c r="D5" t="n">
-        <v>6.589754006152781</v>
+        <v>6.014654248564055</v>
       </c>
       <c r="E5" t="n">
-        <v>14.08122998107844</v>
+        <v>12.31985994184179</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.727474454713992</v>
+        <v>1.287111552080052</v>
       </c>
       <c r="C6" t="n">
-        <v>6.821691875901328</v>
+        <v>6.002381056161827</v>
       </c>
       <c r="D6" t="n">
-        <v>6.851072610912219</v>
+        <v>6.313189326918261</v>
       </c>
       <c r="E6" t="n">
-        <v>15.40023894152754</v>
+        <v>13.60268193516014</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.946997408990845</v>
+        <v>1.411902524867755</v>
       </c>
       <c r="C7" t="n">
-        <v>7.862417781281783</v>
+        <v>7.074157848789279</v>
       </c>
       <c r="D7" t="n">
-        <v>7.164541217658655</v>
+        <v>6.647299430513963</v>
       </c>
       <c r="E7" t="n">
-        <v>16.97395640793128</v>
+        <v>15.133359804171</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.176493514025439</v>
+        <v>1.542592720800303</v>
       </c>
       <c r="C8" t="n">
-        <v>5.499198893409406</v>
+        <v>8.344573807809736</v>
       </c>
       <c r="D8" t="n">
-        <v>5.354536932625349</v>
+        <v>7.016548889269798</v>
       </c>
       <c r="E8" t="n">
-        <v>12.03022934006019</v>
+        <v>16.90371541787984</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.477173753801316</v>
+        <v>1.660006923135971</v>
       </c>
       <c r="C9" t="n">
-        <v>6.78363695600816</v>
+        <v>9.816820707421249</v>
       </c>
       <c r="D9" t="n">
-        <v>5.750621659227147</v>
+        <v>7.461295069732764</v>
       </c>
       <c r="E9" t="n">
-        <v>14.01143236903662</v>
+        <v>18.93812270028998</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.79646861530909</v>
+        <v>1.034222119038802</v>
       </c>
       <c r="C10" t="n">
-        <v>8.258904885347199</v>
+        <v>7.261771783818722</v>
       </c>
       <c r="D10" t="n">
-        <v>6.140876723851357</v>
+        <v>5.890505860434947</v>
       </c>
       <c r="E10" t="n">
-        <v>16.19625022450765</v>
+        <v>14.18649976329247</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.132300036335171</v>
+        <v>0.9638602610754337</v>
       </c>
       <c r="C11" t="n">
-        <v>9.838521940165897</v>
+        <v>7.954070812422446</v>
       </c>
       <c r="D11" t="n">
-        <v>6.508057546410671</v>
+        <v>5.748662952125368</v>
       </c>
       <c r="E11" t="n">
-        <v>18.47887952291174</v>
+        <v>14.66659402562325</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.476699598053225</v>
+        <v>1.031620487622548</v>
       </c>
       <c r="C12" t="n">
-        <v>11.53003969861251</v>
+        <v>9.655586846037806</v>
       </c>
       <c r="D12" t="n">
-        <v>6.855018916782383</v>
+        <v>6.15292702178012</v>
       </c>
       <c r="E12" t="n">
-        <v>20.86175821344812</v>
+        <v>16.84013435544048</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.814345999524695</v>
+        <v>0.805946142847334</v>
       </c>
       <c r="C13" t="n">
-        <v>13.28915698231975</v>
+        <v>9.430030310987101</v>
       </c>
       <c r="D13" t="n">
-        <v>7.32220485336226</v>
+        <v>5.613338848571988</v>
       </c>
       <c r="E13" t="n">
-        <v>23.42570783520671</v>
+        <v>15.84931530240642</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.621179618976843</v>
+        <v>0.8645957506990384</v>
       </c>
       <c r="C14" t="n">
-        <v>9.349497546807733</v>
+        <v>11.25683698661844</v>
       </c>
       <c r="D14" t="n">
-        <v>5.557654118787108</v>
+        <v>5.990261244663466</v>
       </c>
       <c r="E14" t="n">
-        <v>16.52833128457168</v>
+        <v>18.11169398198095</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.673879835740812</v>
+        <v>0.8311672413694347</v>
       </c>
       <c r="C15" t="n">
-        <v>10.15700466850482</v>
+        <v>12.33648457193274</v>
       </c>
       <c r="D15" t="n">
-        <v>5.51247408943767</v>
+        <v>6.040477639735689</v>
       </c>
       <c r="E15" t="n">
-        <v>17.3433585936833</v>
+        <v>19.20812945303786</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.949937472697972</v>
+        <v>0.8987900232379549</v>
       </c>
       <c r="C16" t="n">
-        <v>12.04119449744938</v>
+        <v>14.45773701902178</v>
       </c>
       <c r="D16" t="n">
-        <v>5.926054944805725</v>
+        <v>6.41072415143829</v>
       </c>
       <c r="E16" t="n">
-        <v>19.91718691495308</v>
+        <v>21.76725119369802</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.568508854644002</v>
+        <v>0.5356611823911448</v>
       </c>
       <c r="C17" t="n">
-        <v>11.08725970566389</v>
+        <v>10.83297723278692</v>
       </c>
       <c r="D17" t="n">
-        <v>5.455395277912761</v>
+        <v>5.324479221551448</v>
       </c>
       <c r="E17" t="n">
-        <v>18.11116383822065</v>
+        <v>16.69311763672951</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.792376783643402</v>
+        <v>0.4135514029369264</v>
       </c>
       <c r="C18" t="n">
-        <v>13.0200067760605</v>
+        <v>9.864728559473503</v>
       </c>
       <c r="D18" t="n">
-        <v>5.803660458517275</v>
+        <v>4.842745440554581</v>
       </c>
       <c r="E18" t="n">
-        <v>20.61604401822117</v>
+        <v>15.12102540296501</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.799396279728767</v>
+        <v>0.4774239085752239</v>
       </c>
       <c r="C19" t="n">
-        <v>13.99512768330364</v>
+        <v>12.14266794016033</v>
       </c>
       <c r="D19" t="n">
-        <v>5.854662251752896</v>
+        <v>5.329446864934938</v>
       </c>
       <c r="E19" t="n">
-        <v>21.6491862147853</v>
+        <v>17.9495387136705</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.004571732439307</v>
+        <v>0.5409626199940776</v>
       </c>
       <c r="C20" t="n">
-        <v>16.1722121223332</v>
+        <v>14.44023245745506</v>
       </c>
       <c r="D20" t="n">
-        <v>6.254979695636576</v>
+        <v>5.752776475006162</v>
       </c>
       <c r="E20" t="n">
-        <v>24.43176355040908</v>
+        <v>20.7339715524553</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.190388726353343</v>
+        <v>0.5972756683096745</v>
       </c>
       <c r="C21" t="n">
-        <v>11.96747506233749</v>
+        <v>16.6709203211365</v>
       </c>
       <c r="D21" t="n">
-        <v>5.202290902280891</v>
+        <v>6.153977491823664</v>
       </c>
       <c r="E21" t="n">
-        <v>18.36015469097173</v>
+        <v>23.42217348126983</v>
       </c>
     </row>
   </sheetData>
